--- a/roadmap.xlsx
+++ b/roadmap.xlsx
@@ -45,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00ff9232"/>
         <bgColor rgb="00ff9232"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffa251"/>
+        <bgColor rgb="00ffa251"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -261,28 +267,11 @@
       </right>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="002E7D32"/>
-      </left>
-      <right style="medium">
-        <color rgb="00D32F2F"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002E7D32"/>
-      </left>
-      <right style="medium">
-        <color rgb="00D32F2F"/>
-      </right>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -307,73 +296,83 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -739,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB55"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -805,7 +804,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -825,7 +824,7 @@
           <t>May 2026</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
@@ -937,119 +936,119 @@
           <t>R22</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>R22</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>R2</t>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>R24</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="Y3" s="5" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="AA3" s="5" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="AB3" s="5" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R29</t>
         </is>
       </c>
     </row>
@@ -1071,11 +1070,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr"/>
       <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
       <c r="H4" s="9" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
       <c r="K4" s="9" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr"/>
       <c r="M4" s="9" t="inlineStr"/>
@@ -1113,11 +1112,11 @@
       </c>
       <c r="D5" s="14" t="n"/>
       <c r="E5" s="15" t="inlineStr"/>
-      <c r="F5" s="16" t="inlineStr"/>
+      <c r="F5" s="15" t="inlineStr"/>
       <c r="G5" s="15" t="inlineStr"/>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="14" t="n"/>
-      <c r="J5" s="14" t="n"/>
+      <c r="J5" s="16" t="n"/>
       <c r="K5" s="14" t="n"/>
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="14" t="n"/>
@@ -1147,11 +1146,11 @@
       </c>
       <c r="D6" s="14" t="n"/>
       <c r="E6" s="14" t="n"/>
-      <c r="F6" s="17" t="n"/>
+      <c r="F6" s="14" t="n"/>
       <c r="G6" s="15" t="inlineStr"/>
       <c r="H6" s="15" t="inlineStr"/>
       <c r="I6" s="15" t="inlineStr"/>
-      <c r="J6" s="14" t="n"/>
+      <c r="J6" s="16" t="n"/>
       <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="14" t="n"/>
@@ -1181,11 +1180,11 @@
       </c>
       <c r="D7" s="14" t="n"/>
       <c r="E7" s="14" t="n"/>
-      <c r="F7" s="17" t="n"/>
+      <c r="F7" s="14" t="n"/>
       <c r="G7" s="14" t="n"/>
       <c r="H7" s="14" t="n"/>
       <c r="I7" s="15" t="inlineStr"/>
-      <c r="J7" s="15" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
       <c r="K7" s="15" t="inlineStr"/>
       <c r="L7" s="15" t="inlineStr"/>
       <c r="M7" s="15" t="inlineStr"/>
@@ -1215,11 +1214,11 @@
       </c>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
-      <c r="F8" s="20" t="n"/>
+      <c r="F8" s="18" t="n"/>
       <c r="G8" s="18" t="n"/>
       <c r="H8" s="18" t="n"/>
       <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
+      <c r="J8" s="20" t="n"/>
       <c r="K8" s="18" t="n"/>
       <c r="L8" s="21" t="inlineStr"/>
       <c r="M8" s="21" t="inlineStr"/>
@@ -1253,11 +1252,11 @@
       </c>
       <c r="D9" s="14" t="n"/>
       <c r="E9" s="22" t="inlineStr"/>
-      <c r="F9" s="23" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr"/>
       <c r="G9" s="22" t="inlineStr"/>
       <c r="H9" s="14" t="n"/>
       <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
+      <c r="J9" s="16" t="n"/>
       <c r="K9" s="14" t="n"/>
       <c r="L9" s="14" t="n"/>
       <c r="M9" s="14" t="n"/>
@@ -1287,11 +1286,11 @@
       </c>
       <c r="D10" s="14" t="n"/>
       <c r="E10" s="14" t="n"/>
-      <c r="F10" s="17" t="n"/>
+      <c r="F10" s="14" t="n"/>
       <c r="G10" s="22" t="inlineStr"/>
       <c r="H10" s="22" t="inlineStr"/>
       <c r="I10" s="22" t="inlineStr"/>
-      <c r="J10" s="14" t="n"/>
+      <c r="J10" s="16" t="n"/>
       <c r="K10" s="14" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="14" t="n"/>
@@ -1321,11 +1320,11 @@
       </c>
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
-      <c r="F11" s="17" t="n"/>
+      <c r="F11" s="14" t="n"/>
       <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="22" t="inlineStr"/>
-      <c r="J11" s="22" t="inlineStr"/>
+      <c r="J11" s="23" t="inlineStr"/>
       <c r="K11" s="22" t="inlineStr"/>
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="14" t="n"/>
@@ -1346,64 +1345,60 @@
       <c r="AB11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n"/>
-      <c r="B12" s="24" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Tenant X PROD ATO</t>
         </is>
       </c>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="26" t="inlineStr"/>
-      <c r="J12" s="26" t="inlineStr"/>
-      <c r="K12" s="26" t="inlineStr"/>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n"/>
-      <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="24" t="n"/>
-      <c r="R12" s="24" t="n"/>
-      <c r="S12" s="24" t="n"/>
-      <c r="T12" s="24" t="n"/>
-      <c r="U12" s="24" t="n"/>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="24" t="n"/>
-      <c r="X12" s="24" t="n"/>
-      <c r="Y12" s="24" t="n"/>
-      <c r="Z12" s="24" t="n"/>
-      <c r="AA12" s="24" t="n"/>
-      <c r="AB12" s="24" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="24" t="inlineStr"/>
+      <c r="J12" s="25" t="inlineStr"/>
+      <c r="K12" s="24" t="inlineStr"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n"/>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="18" t="n"/>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="18" t="n"/>
+      <c r="U12" s="18" t="n"/>
+      <c r="V12" s="18" t="n"/>
+      <c r="W12" s="18" t="n"/>
+      <c r="X12" s="18" t="n"/>
+      <c r="Y12" s="18" t="n"/>
+      <c r="Z12" s="18" t="n"/>
+      <c r="AA12" s="18" t="n"/>
+      <c r="AB12" s="18" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Core Services</t>
-        </is>
-      </c>
+      <c r="A13" s="14" t="n"/>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Kubernetes (Rancher)</t>
+          <t>Onboarding Tenant Apps</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Rancher RKE1 support</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr"/>
-      <c r="E13" s="28" t="inlineStr"/>
-      <c r="F13" s="29" t="inlineStr"/>
-      <c r="G13" s="28" t="inlineStr"/>
-      <c r="H13" s="28" t="inlineStr"/>
-      <c r="I13" s="28" t="inlineStr"/>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
+          <t>NEW 1</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="26" t="inlineStr"/>
+      <c r="K13" s="27" t="inlineStr"/>
+      <c r="L13" s="27" t="inlineStr"/>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="14" t="n"/>
       <c r="O13" s="14" t="n"/>
@@ -1422,54 +1417,62 @@
       <c r="AB13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Rancher RKE2 development</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr"/>
-      <c r="E14" s="28" t="inlineStr"/>
-      <c r="F14" s="29" t="inlineStr"/>
-      <c r="G14" s="28" t="inlineStr"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="14" t="n"/>
-      <c r="N14" s="14" t="n"/>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="14" t="n"/>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="14" t="n"/>
-      <c r="S14" s="14" t="n"/>
-      <c r="T14" s="14" t="n"/>
-      <c r="U14" s="14" t="n"/>
-      <c r="V14" s="14" t="n"/>
-      <c r="W14" s="14" t="n"/>
-      <c r="X14" s="14" t="n"/>
-      <c r="Y14" s="14" t="n"/>
-      <c r="Z14" s="14" t="n"/>
-      <c r="AA14" s="14" t="n"/>
-      <c r="AB14" s="14" t="n"/>
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>NEW 3</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="29" t="inlineStr"/>
+      <c r="K14" s="30" t="inlineStr"/>
+      <c r="L14" s="30" t="inlineStr"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="28" t="n"/>
+      <c r="O14" s="28" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n"/>
+      <c r="R14" s="28" t="n"/>
+      <c r="S14" s="28" t="n"/>
+      <c r="T14" s="28" t="n"/>
+      <c r="U14" s="28" t="n"/>
+      <c r="V14" s="28" t="n"/>
+      <c r="W14" s="28" t="n"/>
+      <c r="X14" s="28" t="n"/>
+      <c r="Y14" s="28" t="n"/>
+      <c r="Z14" s="28" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n"/>
-      <c r="B15" s="14" t="n"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Core Services</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Kubernetes (Rancher)</t>
+        </is>
+      </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Rancher RKE2 Tenant Migration</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="27" t="inlineStr"/>
-      <c r="I15" s="28" t="inlineStr"/>
-      <c r="J15" s="14" t="n"/>
+          <t>Rancher RKE1 support</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr"/>
+      <c r="E15" s="32" t="inlineStr"/>
+      <c r="F15" s="32" t="inlineStr"/>
+      <c r="G15" s="32" t="inlineStr"/>
+      <c r="H15" s="32" t="inlineStr"/>
+      <c r="I15" s="32" t="inlineStr"/>
+      <c r="J15" s="16" t="n"/>
       <c r="K15" s="14" t="n"/>
       <c r="L15" s="14" t="n"/>
       <c r="M15" s="14" t="n"/>
@@ -1490,58 +1493,54 @@
       <c r="AB15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n"/>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Rancher RKE2 Tenant Support</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="30" t="inlineStr"/>
-      <c r="I16" s="31" t="inlineStr"/>
-      <c r="J16" s="31" t="inlineStr"/>
-      <c r="K16" s="31" t="inlineStr"/>
-      <c r="L16" s="31" t="inlineStr"/>
-      <c r="M16" s="31" t="inlineStr"/>
-      <c r="N16" s="31" t="inlineStr"/>
-      <c r="O16" s="31" t="inlineStr"/>
-      <c r="P16" s="31" t="inlineStr"/>
-      <c r="Q16" s="31" t="inlineStr"/>
-      <c r="R16" s="31" t="inlineStr"/>
-      <c r="S16" s="31" t="inlineStr"/>
-      <c r="T16" s="31" t="inlineStr"/>
-      <c r="U16" s="31" t="inlineStr"/>
-      <c r="V16" s="31" t="inlineStr"/>
-      <c r="W16" s="31" t="inlineStr"/>
-      <c r="X16" s="31" t="inlineStr"/>
-      <c r="Y16" s="31" t="inlineStr"/>
-      <c r="Z16" s="31" t="inlineStr"/>
-      <c r="AA16" s="31" t="inlineStr"/>
-      <c r="AB16" s="31" t="inlineStr"/>
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Rancher RKE2 development</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr"/>
+      <c r="E16" s="32" t="inlineStr"/>
+      <c r="F16" s="32" t="inlineStr"/>
+      <c r="G16" s="32" t="inlineStr"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
+      <c r="T16" s="14" t="n"/>
+      <c r="U16" s="14" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="14" t="n"/>
+      <c r="X16" s="14" t="n"/>
+      <c r="Y16" s="14" t="n"/>
+      <c r="Z16" s="14" t="n"/>
+      <c r="AA16" s="14" t="n"/>
+      <c r="AB16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n"/>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Kubernetes (EKS)</t>
-        </is>
-      </c>
+      <c r="B17" s="14" t="n"/>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>EKS v1 support</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr"/>
-      <c r="E17" s="33" t="inlineStr"/>
-      <c r="F17" s="34" t="inlineStr"/>
-      <c r="G17" s="33" t="inlineStr"/>
-      <c r="H17" s="33" t="inlineStr"/>
-      <c r="I17" s="33" t="inlineStr"/>
-      <c r="J17" s="14" t="n"/>
+          <t>Rancher RKE2 Tenant Migration</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="31" t="inlineStr"/>
+      <c r="I17" s="32" t="inlineStr"/>
+      <c r="J17" s="16" t="n"/>
       <c r="K17" s="14" t="n"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="14" t="n"/>
@@ -1562,54 +1561,58 @@
       <c r="AB17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>AL2023 AMI hardening and STIG</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="32" t="inlineStr"/>
-      <c r="F18" s="34" t="inlineStr"/>
-      <c r="G18" s="33" t="inlineStr"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="14" t="n"/>
-      <c r="S18" s="14" t="n"/>
-      <c r="T18" s="14" t="n"/>
-      <c r="U18" s="14" t="n"/>
-      <c r="V18" s="14" t="n"/>
-      <c r="W18" s="14" t="n"/>
-      <c r="X18" s="14" t="n"/>
-      <c r="Y18" s="14" t="n"/>
-      <c r="Z18" s="14" t="n"/>
-      <c r="AA18" s="14" t="n"/>
-      <c r="AB18" s="14" t="n"/>
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Rancher RKE2 Tenant Support</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="33" t="inlineStr"/>
+      <c r="I18" s="34" t="inlineStr"/>
+      <c r="J18" s="35" t="inlineStr"/>
+      <c r="K18" s="34" t="inlineStr"/>
+      <c r="L18" s="34" t="inlineStr"/>
+      <c r="M18" s="34" t="inlineStr"/>
+      <c r="N18" s="34" t="inlineStr"/>
+      <c r="O18" s="34" t="inlineStr"/>
+      <c r="P18" s="34" t="inlineStr"/>
+      <c r="Q18" s="34" t="inlineStr"/>
+      <c r="R18" s="34" t="inlineStr"/>
+      <c r="S18" s="34" t="inlineStr"/>
+      <c r="T18" s="34" t="inlineStr"/>
+      <c r="U18" s="34" t="inlineStr"/>
+      <c r="V18" s="34" t="inlineStr"/>
+      <c r="W18" s="34" t="inlineStr"/>
+      <c r="X18" s="34" t="inlineStr"/>
+      <c r="Y18" s="34" t="inlineStr"/>
+      <c r="Z18" s="34" t="inlineStr"/>
+      <c r="AA18" s="34" t="inlineStr"/>
+      <c r="AB18" s="34" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n"/>
-      <c r="B19" s="14" t="n"/>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Kubernetes (EKS)</t>
+        </is>
+      </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>EKS v2 config</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="35" t="inlineStr"/>
-      <c r="G19" s="33" t="inlineStr"/>
-      <c r="H19" s="33" t="inlineStr"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
+          <t>EKS v1 support</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr"/>
+      <c r="E19" s="37" t="inlineStr"/>
+      <c r="F19" s="37" t="inlineStr"/>
+      <c r="G19" s="37" t="inlineStr"/>
+      <c r="H19" s="37" t="inlineStr"/>
+      <c r="I19" s="37" t="inlineStr"/>
+      <c r="J19" s="16" t="n"/>
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="14" t="n"/>
@@ -1630,58 +1633,54 @@
       <c r="AB19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n"/>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>Multi-cluster federation</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="36" t="inlineStr"/>
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>AL2023 AMI hardening and STIG</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="36" t="inlineStr"/>
+      <c r="F20" s="37" t="inlineStr"/>
       <c r="G20" s="37" t="inlineStr"/>
-      <c r="H20" s="37" t="inlineStr"/>
-      <c r="I20" s="37" t="inlineStr"/>
-      <c r="J20" s="37" t="inlineStr"/>
-      <c r="K20" s="37" t="inlineStr"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="18" t="n"/>
-      <c r="O20" s="18" t="n"/>
-      <c r="P20" s="18" t="n"/>
-      <c r="Q20" s="18" t="n"/>
-      <c r="R20" s="18" t="n"/>
-      <c r="S20" s="18" t="n"/>
-      <c r="T20" s="18" t="n"/>
-      <c r="U20" s="18" t="n"/>
-      <c r="V20" s="18" t="n"/>
-      <c r="W20" s="18" t="n"/>
-      <c r="X20" s="18" t="n"/>
-      <c r="Y20" s="18" t="n"/>
-      <c r="Z20" s="18" t="n"/>
-      <c r="AA20" s="18" t="n"/>
-      <c r="AB20" s="18" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="n"/>
+      <c r="T20" s="14" t="n"/>
+      <c r="U20" s="14" t="n"/>
+      <c r="V20" s="14" t="n"/>
+      <c r="W20" s="14" t="n"/>
+      <c r="X20" s="14" t="n"/>
+      <c r="Y20" s="14" t="n"/>
+      <c r="Z20" s="14" t="n"/>
+      <c r="AA20" s="14" t="n"/>
+      <c r="AB20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Kubernetes (EKS Auto)</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="n"/>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>EKS Auto Discovery</t>
+          <t>EKS v2 config</t>
         </is>
       </c>
       <c r="D21" s="14" t="n"/>
       <c r="E21" s="14" t="n"/>
-      <c r="F21" s="38" t="inlineStr"/>
-      <c r="G21" s="39" t="inlineStr"/>
-      <c r="H21" s="39" t="inlineStr"/>
+      <c r="F21" s="36" t="inlineStr"/>
+      <c r="G21" s="37" t="inlineStr"/>
+      <c r="H21" s="37" t="inlineStr"/>
       <c r="I21" s="14" t="n"/>
-      <c r="J21" s="14" t="n"/>
+      <c r="J21" s="16" t="n"/>
       <c r="K21" s="14" t="n"/>
       <c r="L21" s="14" t="n"/>
       <c r="M21" s="14" t="n"/>
@@ -1706,17 +1705,17 @@
       <c r="B22" s="18" t="n"/>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>EKS Auto Platform Implementation</t>
+          <t>Multi-cluster federation</t>
         </is>
       </c>
       <c r="D22" s="18" t="n"/>
       <c r="E22" s="18" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="40" t="inlineStr"/>
-      <c r="I22" s="40" t="inlineStr"/>
+      <c r="F22" s="38" t="inlineStr"/>
+      <c r="G22" s="39" t="inlineStr"/>
+      <c r="H22" s="39" t="inlineStr"/>
+      <c r="I22" s="39" t="inlineStr"/>
       <c r="J22" s="40" t="inlineStr"/>
-      <c r="K22" s="18" t="n"/>
+      <c r="K22" s="39" t="inlineStr"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
       <c r="N22" s="18" t="n"/>
@@ -1739,21 +1738,21 @@
       <c r="A23" s="14" t="n"/>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Observability</t>
+          <t>Kubernetes (EKS Auto)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Elastic Support</t>
-        </is>
-      </c>
-      <c r="D23" s="41" t="inlineStr"/>
-      <c r="E23" s="42" t="inlineStr"/>
-      <c r="F23" s="43" t="inlineStr"/>
-      <c r="G23" s="42" t="inlineStr"/>
-      <c r="H23" s="42" t="inlineStr"/>
-      <c r="I23" s="42" t="inlineStr"/>
-      <c r="J23" s="14" t="n"/>
+          <t>EKS Auto Discovery</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="41" t="inlineStr"/>
+      <c r="G23" s="41" t="inlineStr"/>
+      <c r="H23" s="41" t="inlineStr"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="16" t="n"/>
       <c r="K23" s="14" t="n"/>
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="14" t="n"/>
@@ -1774,54 +1773,58 @@
       <c r="AB23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Prometheus/Grafana Support</t>
-        </is>
-      </c>
-      <c r="D24" s="44" t="inlineStr"/>
-      <c r="E24" s="42" t="inlineStr"/>
-      <c r="F24" s="43" t="inlineStr"/>
-      <c r="G24" s="42" t="inlineStr"/>
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>EKS Auto Platform Implementation</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
       <c r="H24" s="42" t="inlineStr"/>
       <c r="I24" s="42" t="inlineStr"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="14" t="n"/>
-      <c r="R24" s="14" t="n"/>
-      <c r="S24" s="14" t="n"/>
-      <c r="T24" s="14" t="n"/>
-      <c r="U24" s="14" t="n"/>
-      <c r="V24" s="14" t="n"/>
-      <c r="W24" s="14" t="n"/>
-      <c r="X24" s="14" t="n"/>
-      <c r="Y24" s="14" t="n"/>
-      <c r="Z24" s="14" t="n"/>
-      <c r="AA24" s="14" t="n"/>
-      <c r="AB24" s="14" t="n"/>
+      <c r="J24" s="43" t="inlineStr"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
+      <c r="P24" s="18" t="n"/>
+      <c r="Q24" s="18" t="n"/>
+      <c r="R24" s="18" t="n"/>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="18" t="n"/>
+      <c r="U24" s="18" t="n"/>
+      <c r="V24" s="18" t="n"/>
+      <c r="W24" s="18" t="n"/>
+      <c r="X24" s="18" t="n"/>
+      <c r="Y24" s="18" t="n"/>
+      <c r="Z24" s="18" t="n"/>
+      <c r="AA24" s="18" t="n"/>
+      <c r="AB24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n"/>
-      <c r="B25" s="14" t="n"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Observability</t>
+        </is>
+      </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Prometheus/Grafana Add-ons</t>
+          <t>Elastic Support</t>
         </is>
       </c>
       <c r="D25" s="44" t="inlineStr"/>
-      <c r="E25" s="42" t="inlineStr"/>
-      <c r="F25" s="43" t="inlineStr"/>
-      <c r="G25" s="42" t="inlineStr"/>
-      <c r="H25" s="42" t="inlineStr"/>
-      <c r="I25" s="42" t="inlineStr"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="E25" s="45" t="inlineStr"/>
+      <c r="F25" s="45" t="inlineStr"/>
+      <c r="G25" s="45" t="inlineStr"/>
+      <c r="H25" s="45" t="inlineStr"/>
+      <c r="I25" s="45" t="inlineStr"/>
+      <c r="J25" s="16" t="n"/>
       <c r="K25" s="14" t="n"/>
       <c r="L25" s="14" t="n"/>
       <c r="M25" s="14" t="n"/>
@@ -1846,156 +1849,156 @@
       <c r="B26" s="14" t="n"/>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Elastic Support</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="44" t="inlineStr"/>
-      <c r="J26" s="42" t="inlineStr"/>
-      <c r="K26" s="42" t="inlineStr"/>
-      <c r="L26" s="42" t="inlineStr"/>
-      <c r="M26" s="42" t="inlineStr"/>
-      <c r="N26" s="42" t="inlineStr"/>
-      <c r="O26" s="42" t="inlineStr"/>
-      <c r="P26" s="42" t="inlineStr"/>
-      <c r="Q26" s="42" t="inlineStr"/>
-      <c r="R26" s="42" t="inlineStr"/>
-      <c r="S26" s="42" t="inlineStr"/>
-      <c r="T26" s="42" t="inlineStr"/>
-      <c r="U26" s="42" t="inlineStr"/>
-      <c r="V26" s="42" t="inlineStr"/>
-      <c r="W26" s="42" t="inlineStr"/>
-      <c r="X26" s="42" t="inlineStr"/>
-      <c r="Y26" s="42" t="inlineStr"/>
-      <c r="Z26" s="42" t="inlineStr"/>
-      <c r="AA26" s="42" t="inlineStr"/>
-      <c r="AB26" s="42" t="inlineStr"/>
+          <t>Prometheus/Grafana Support</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr"/>
+      <c r="E26" s="45" t="inlineStr"/>
+      <c r="F26" s="45" t="inlineStr"/>
+      <c r="G26" s="45" t="inlineStr"/>
+      <c r="H26" s="45" t="inlineStr"/>
+      <c r="I26" s="45" t="inlineStr"/>
+      <c r="J26" s="16" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
+      <c r="O26" s="14" t="n"/>
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="14" t="n"/>
+      <c r="S26" s="14" t="n"/>
+      <c r="T26" s="14" t="n"/>
+      <c r="U26" s="14" t="n"/>
+      <c r="V26" s="14" t="n"/>
+      <c r="W26" s="14" t="n"/>
+      <c r="X26" s="14" t="n"/>
+      <c r="Y26" s="14" t="n"/>
+      <c r="Z26" s="14" t="n"/>
+      <c r="AA26" s="14" t="n"/>
+      <c r="AB26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n"/>
-      <c r="B27" s="18" t="n"/>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>Prometheus/Grafana Support</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Prometheus/Grafana Add-ons</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr"/>
+      <c r="E27" s="45" t="inlineStr"/>
+      <c r="F27" s="45" t="inlineStr"/>
+      <c r="G27" s="45" t="inlineStr"/>
+      <c r="H27" s="45" t="inlineStr"/>
       <c r="I27" s="45" t="inlineStr"/>
-      <c r="J27" s="46" t="inlineStr"/>
-      <c r="K27" s="46" t="inlineStr"/>
-      <c r="L27" s="46" t="inlineStr"/>
-      <c r="M27" s="46" t="inlineStr"/>
-      <c r="N27" s="46" t="inlineStr"/>
-      <c r="O27" s="46" t="inlineStr"/>
-      <c r="P27" s="46" t="inlineStr"/>
-      <c r="Q27" s="46" t="inlineStr"/>
-      <c r="R27" s="46" t="inlineStr"/>
-      <c r="S27" s="46" t="inlineStr"/>
-      <c r="T27" s="46" t="inlineStr"/>
-      <c r="U27" s="46" t="inlineStr"/>
-      <c r="V27" s="46" t="inlineStr"/>
-      <c r="W27" s="46" t="inlineStr"/>
-      <c r="X27" s="46" t="inlineStr"/>
-      <c r="Y27" s="46" t="inlineStr"/>
-      <c r="Z27" s="46" t="inlineStr"/>
-      <c r="AA27" s="46" t="inlineStr"/>
-      <c r="AB27" s="46" t="inlineStr"/>
+      <c r="J27" s="16" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+      <c r="N27" s="14" t="n"/>
+      <c r="O27" s="14" t="n"/>
+      <c r="P27" s="14" t="n"/>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="14" t="n"/>
+      <c r="S27" s="14" t="n"/>
+      <c r="T27" s="14" t="n"/>
+      <c r="U27" s="14" t="n"/>
+      <c r="V27" s="14" t="n"/>
+      <c r="W27" s="14" t="n"/>
+      <c r="X27" s="14" t="n"/>
+      <c r="Y27" s="14" t="n"/>
+      <c r="Z27" s="14" t="n"/>
+      <c r="AA27" s="14" t="n"/>
+      <c r="AB27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n"/>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>OAuth</t>
-        </is>
-      </c>
+      <c r="B28" s="14" t="n"/>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Keycloak OAUTH2 Support</t>
-        </is>
-      </c>
-      <c r="D28" s="47" t="inlineStr"/>
-      <c r="E28" s="48" t="inlineStr"/>
-      <c r="F28" s="49" t="inlineStr"/>
-      <c r="G28" s="48" t="inlineStr"/>
-      <c r="H28" s="48" t="inlineStr"/>
-      <c r="I28" s="48" t="inlineStr"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="14" t="n"/>
-      <c r="M28" s="14" t="n"/>
-      <c r="N28" s="14" t="n"/>
-      <c r="O28" s="14" t="n"/>
-      <c r="P28" s="14" t="n"/>
-      <c r="Q28" s="14" t="n"/>
-      <c r="R28" s="14" t="n"/>
-      <c r="S28" s="14" t="n"/>
-      <c r="T28" s="14" t="n"/>
-      <c r="U28" s="14" t="n"/>
-      <c r="V28" s="14" t="n"/>
-      <c r="W28" s="14" t="n"/>
-      <c r="X28" s="14" t="n"/>
-      <c r="Y28" s="14" t="n"/>
-      <c r="Z28" s="14" t="n"/>
-      <c r="AA28" s="14" t="n"/>
-      <c r="AB28" s="14" t="n"/>
+          <t>Elastic Support</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="46" t="inlineStr"/>
+      <c r="J28" s="47" t="inlineStr"/>
+      <c r="K28" s="45" t="inlineStr"/>
+      <c r="L28" s="45" t="inlineStr"/>
+      <c r="M28" s="45" t="inlineStr"/>
+      <c r="N28" s="45" t="inlineStr"/>
+      <c r="O28" s="45" t="inlineStr"/>
+      <c r="P28" s="45" t="inlineStr"/>
+      <c r="Q28" s="45" t="inlineStr"/>
+      <c r="R28" s="45" t="inlineStr"/>
+      <c r="S28" s="45" t="inlineStr"/>
+      <c r="T28" s="45" t="inlineStr"/>
+      <c r="U28" s="45" t="inlineStr"/>
+      <c r="V28" s="45" t="inlineStr"/>
+      <c r="W28" s="45" t="inlineStr"/>
+      <c r="X28" s="45" t="inlineStr"/>
+      <c r="Y28" s="45" t="inlineStr"/>
+      <c r="Z28" s="45" t="inlineStr"/>
+      <c r="AA28" s="45" t="inlineStr"/>
+      <c r="AB28" s="45" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n"/>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>F5 Support</t>
-        </is>
-      </c>
-      <c r="D29" s="50" t="inlineStr"/>
-      <c r="E29" s="48" t="inlineStr"/>
-      <c r="F29" s="49" t="inlineStr"/>
-      <c r="G29" s="48" t="inlineStr"/>
-      <c r="H29" s="48" t="inlineStr"/>
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Prometheus/Grafana Support</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
       <c r="I29" s="48" t="inlineStr"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="14" t="n"/>
-      <c r="N29" s="14" t="n"/>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="14" t="n"/>
-      <c r="Q29" s="14" t="n"/>
-      <c r="R29" s="14" t="n"/>
-      <c r="S29" s="14" t="n"/>
-      <c r="T29" s="14" t="n"/>
-      <c r="U29" s="14" t="n"/>
-      <c r="V29" s="14" t="n"/>
-      <c r="W29" s="14" t="n"/>
-      <c r="X29" s="14" t="n"/>
-      <c r="Y29" s="14" t="n"/>
-      <c r="Z29" s="14" t="n"/>
-      <c r="AA29" s="14" t="n"/>
-      <c r="AB29" s="14" t="n"/>
+      <c r="J29" s="49" t="inlineStr"/>
+      <c r="K29" s="50" t="inlineStr"/>
+      <c r="L29" s="50" t="inlineStr"/>
+      <c r="M29" s="50" t="inlineStr"/>
+      <c r="N29" s="50" t="inlineStr"/>
+      <c r="O29" s="50" t="inlineStr"/>
+      <c r="P29" s="50" t="inlineStr"/>
+      <c r="Q29" s="50" t="inlineStr"/>
+      <c r="R29" s="50" t="inlineStr"/>
+      <c r="S29" s="50" t="inlineStr"/>
+      <c r="T29" s="50" t="inlineStr"/>
+      <c r="U29" s="50" t="inlineStr"/>
+      <c r="V29" s="50" t="inlineStr"/>
+      <c r="W29" s="50" t="inlineStr"/>
+      <c r="X29" s="50" t="inlineStr"/>
+      <c r="Y29" s="50" t="inlineStr"/>
+      <c r="Z29" s="50" t="inlineStr"/>
+      <c r="AA29" s="50" t="inlineStr"/>
+      <c r="AB29" s="50" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n"/>
-      <c r="B30" s="14" t="n"/>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>OAuth</t>
+        </is>
+      </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>F5/DEX/OAUTH2 Developmment</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="47" t="inlineStr"/>
-      <c r="F30" s="49" t="inlineStr"/>
-      <c r="G30" s="48" t="inlineStr"/>
-      <c r="H30" s="48" t="inlineStr"/>
-      <c r="I30" s="48" t="inlineStr"/>
-      <c r="J30" s="14" t="n"/>
+          <t>Keycloak OAUTH2 Support</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="inlineStr"/>
+      <c r="E30" s="52" t="inlineStr"/>
+      <c r="F30" s="52" t="inlineStr"/>
+      <c r="G30" s="52" t="inlineStr"/>
+      <c r="H30" s="52" t="inlineStr"/>
+      <c r="I30" s="52" t="inlineStr"/>
+      <c r="J30" s="16" t="n"/>
       <c r="K30" s="14" t="n"/>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="14" t="n"/>
@@ -2020,228 +2023,228 @@
       <c r="B31" s="14" t="n"/>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>F5/DEX/OAUTH2 Support</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="47" t="inlineStr"/>
-      <c r="J31" s="48" t="inlineStr"/>
-      <c r="K31" s="48" t="inlineStr"/>
-      <c r="L31" s="48" t="inlineStr"/>
-      <c r="M31" s="48" t="inlineStr"/>
-      <c r="N31" s="48" t="inlineStr"/>
-      <c r="O31" s="48" t="inlineStr"/>
-      <c r="P31" s="48" t="inlineStr"/>
-      <c r="Q31" s="48" t="inlineStr"/>
-      <c r="R31" s="48" t="inlineStr"/>
-      <c r="S31" s="48" t="inlineStr"/>
-      <c r="T31" s="48" t="inlineStr"/>
-      <c r="U31" s="48" t="inlineStr"/>
-      <c r="V31" s="48" t="inlineStr"/>
-      <c r="W31" s="48" t="inlineStr"/>
-      <c r="X31" s="48" t="inlineStr"/>
-      <c r="Y31" s="48" t="inlineStr"/>
-      <c r="Z31" s="48" t="inlineStr"/>
-      <c r="AA31" s="48" t="inlineStr"/>
-      <c r="AB31" s="48" t="inlineStr"/>
+          <t>F5 Support</t>
+        </is>
+      </c>
+      <c r="D31" s="53" t="inlineStr"/>
+      <c r="E31" s="52" t="inlineStr"/>
+      <c r="F31" s="52" t="inlineStr"/>
+      <c r="G31" s="52" t="inlineStr"/>
+      <c r="H31" s="52" t="inlineStr"/>
+      <c r="I31" s="52" t="inlineStr"/>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+      <c r="N31" s="14" t="n"/>
+      <c r="O31" s="14" t="n"/>
+      <c r="P31" s="14" t="n"/>
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="14" t="n"/>
+      <c r="S31" s="14" t="n"/>
+      <c r="T31" s="14" t="n"/>
+      <c r="U31" s="14" t="n"/>
+      <c r="V31" s="14" t="n"/>
+      <c r="W31" s="14" t="n"/>
+      <c r="X31" s="14" t="n"/>
+      <c r="Y31" s="14" t="n"/>
+      <c r="Z31" s="14" t="n"/>
+      <c r="AA31" s="14" t="n"/>
+      <c r="AB31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n"/>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>F5/DEX/OAUTH2 Support</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="20" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="51" t="inlineStr"/>
-      <c r="J32" s="52" t="inlineStr"/>
-      <c r="K32" s="52" t="inlineStr"/>
-      <c r="L32" s="52" t="inlineStr"/>
-      <c r="M32" s="52" t="inlineStr"/>
-      <c r="N32" s="52" t="inlineStr"/>
-      <c r="O32" s="52" t="inlineStr"/>
-      <c r="P32" s="52" t="inlineStr"/>
-      <c r="Q32" s="52" t="inlineStr"/>
-      <c r="R32" s="52" t="inlineStr"/>
-      <c r="S32" s="52" t="inlineStr"/>
-      <c r="T32" s="52" t="inlineStr"/>
-      <c r="U32" s="52" t="inlineStr"/>
-      <c r="V32" s="52" t="inlineStr"/>
-      <c r="W32" s="52" t="inlineStr"/>
-      <c r="X32" s="52" t="inlineStr"/>
-      <c r="Y32" s="52" t="inlineStr"/>
-      <c r="Z32" s="52" t="inlineStr"/>
-      <c r="AA32" s="52" t="inlineStr"/>
-      <c r="AB32" s="52" t="inlineStr"/>
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>F5/DEX/OAUTH2 Developmment</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="51" t="inlineStr"/>
+      <c r="F32" s="52" t="inlineStr"/>
+      <c r="G32" s="52" t="inlineStr"/>
+      <c r="H32" s="52" t="inlineStr"/>
+      <c r="I32" s="52" t="inlineStr"/>
+      <c r="J32" s="16" t="n"/>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14" t="n"/>
+      <c r="O32" s="14" t="n"/>
+      <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14" t="n"/>
+      <c r="R32" s="14" t="n"/>
+      <c r="S32" s="14" t="n"/>
+      <c r="T32" s="14" t="n"/>
+      <c r="U32" s="14" t="n"/>
+      <c r="V32" s="14" t="n"/>
+      <c r="W32" s="14" t="n"/>
+      <c r="X32" s="14" t="n"/>
+      <c r="Y32" s="14" t="n"/>
+      <c r="Z32" s="14" t="n"/>
+      <c r="AA32" s="14" t="n"/>
+      <c r="AB32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n"/>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>CICD</t>
-        </is>
-      </c>
+      <c r="B33" s="14" t="n"/>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>GitLab Support</t>
-        </is>
-      </c>
-      <c r="D33" s="53" t="inlineStr"/>
-      <c r="E33" s="54" t="inlineStr"/>
-      <c r="F33" s="55" t="inlineStr"/>
-      <c r="G33" s="54" t="inlineStr"/>
-      <c r="H33" s="54" t="inlineStr"/>
-      <c r="I33" s="54" t="inlineStr"/>
+          <t>F5/DEX/OAUTH2 Support</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="51" t="inlineStr"/>
       <c r="J33" s="54" t="inlineStr"/>
-      <c r="K33" s="54" t="inlineStr"/>
-      <c r="L33" s="54" t="inlineStr"/>
-      <c r="M33" s="54" t="inlineStr"/>
-      <c r="N33" s="54" t="inlineStr"/>
-      <c r="O33" s="54" t="inlineStr"/>
-      <c r="P33" s="54" t="inlineStr"/>
-      <c r="Q33" s="54" t="inlineStr"/>
-      <c r="R33" s="54" t="inlineStr"/>
-      <c r="S33" s="54" t="inlineStr"/>
-      <c r="T33" s="54" t="inlineStr"/>
-      <c r="U33" s="54" t="inlineStr"/>
-      <c r="V33" s="54" t="inlineStr"/>
-      <c r="W33" s="54" t="inlineStr"/>
-      <c r="X33" s="54" t="inlineStr"/>
-      <c r="Y33" s="54" t="inlineStr"/>
-      <c r="Z33" s="54" t="inlineStr"/>
-      <c r="AA33" s="54" t="inlineStr"/>
-      <c r="AB33" s="54" t="inlineStr"/>
+      <c r="K33" s="52" t="inlineStr"/>
+      <c r="L33" s="52" t="inlineStr"/>
+      <c r="M33" s="52" t="inlineStr"/>
+      <c r="N33" s="52" t="inlineStr"/>
+      <c r="O33" s="52" t="inlineStr"/>
+      <c r="P33" s="52" t="inlineStr"/>
+      <c r="Q33" s="52" t="inlineStr"/>
+      <c r="R33" s="52" t="inlineStr"/>
+      <c r="S33" s="52" t="inlineStr"/>
+      <c r="T33" s="52" t="inlineStr"/>
+      <c r="U33" s="52" t="inlineStr"/>
+      <c r="V33" s="52" t="inlineStr"/>
+      <c r="W33" s="52" t="inlineStr"/>
+      <c r="X33" s="52" t="inlineStr"/>
+      <c r="Y33" s="52" t="inlineStr"/>
+      <c r="Z33" s="52" t="inlineStr"/>
+      <c r="AA33" s="52" t="inlineStr"/>
+      <c r="AB33" s="52" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n"/>
       <c r="B34" s="18" t="n"/>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>Bitbucket -&gt; GitLab Migration</t>
+          <t>F5/DEX/OAUTH2 Support</t>
         </is>
       </c>
       <c r="D34" s="18" t="n"/>
       <c r="E34" s="18" t="n"/>
-      <c r="F34" s="20" t="n"/>
+      <c r="F34" s="18" t="n"/>
       <c r="G34" s="18" t="n"/>
       <c r="H34" s="18" t="n"/>
-      <c r="I34" s="18" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="18" t="n"/>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="56" t="inlineStr"/>
-      <c r="N34" s="56" t="inlineStr"/>
-      <c r="O34" s="56" t="inlineStr"/>
-      <c r="P34" s="56" t="inlineStr"/>
-      <c r="Q34" s="56" t="inlineStr"/>
-      <c r="R34" s="56" t="inlineStr"/>
-      <c r="S34" s="56" t="inlineStr"/>
-      <c r="T34" s="56" t="inlineStr"/>
-      <c r="U34" s="56" t="inlineStr"/>
-      <c r="V34" s="18" t="n"/>
-      <c r="W34" s="18" t="n"/>
-      <c r="X34" s="18" t="n"/>
-      <c r="Y34" s="18" t="n"/>
-      <c r="Z34" s="18" t="n"/>
-      <c r="AA34" s="18" t="n"/>
-      <c r="AB34" s="18" t="n"/>
+      <c r="I34" s="55" t="inlineStr"/>
+      <c r="J34" s="56" t="inlineStr"/>
+      <c r="K34" s="57" t="inlineStr"/>
+      <c r="L34" s="57" t="inlineStr"/>
+      <c r="M34" s="57" t="inlineStr"/>
+      <c r="N34" s="57" t="inlineStr"/>
+      <c r="O34" s="57" t="inlineStr"/>
+      <c r="P34" s="57" t="inlineStr"/>
+      <c r="Q34" s="57" t="inlineStr"/>
+      <c r="R34" s="57" t="inlineStr"/>
+      <c r="S34" s="57" t="inlineStr"/>
+      <c r="T34" s="57" t="inlineStr"/>
+      <c r="U34" s="57" t="inlineStr"/>
+      <c r="V34" s="57" t="inlineStr"/>
+      <c r="W34" s="57" t="inlineStr"/>
+      <c r="X34" s="57" t="inlineStr"/>
+      <c r="Y34" s="57" t="inlineStr"/>
+      <c r="Z34" s="57" t="inlineStr"/>
+      <c r="AA34" s="57" t="inlineStr"/>
+      <c r="AB34" s="57" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Image Repository</t>
+          <t>CICD</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Harbor Implementation (CY failover)</t>
-        </is>
-      </c>
-      <c r="D35" s="57" t="inlineStr"/>
-      <c r="E35" s="57" t="inlineStr"/>
-      <c r="F35" s="58" t="inlineStr"/>
-      <c r="G35" s="57" t="inlineStr"/>
-      <c r="H35" s="14" t="n"/>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="14" t="n"/>
-      <c r="K35" s="14" t="n"/>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="14" t="n"/>
-      <c r="N35" s="14" t="n"/>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="14" t="n"/>
-      <c r="Q35" s="14" t="n"/>
-      <c r="R35" s="14" t="n"/>
-      <c r="S35" s="14" t="n"/>
-      <c r="T35" s="14" t="n"/>
-      <c r="U35" s="14" t="n"/>
-      <c r="V35" s="14" t="n"/>
-      <c r="W35" s="14" t="n"/>
-      <c r="X35" s="14" t="n"/>
-      <c r="Y35" s="14" t="n"/>
-      <c r="Z35" s="14" t="n"/>
-      <c r="AA35" s="14" t="n"/>
-      <c r="AB35" s="14" t="n"/>
+          <t>GitLab Support</t>
+        </is>
+      </c>
+      <c r="D35" s="58" t="inlineStr"/>
+      <c r="E35" s="59" t="inlineStr"/>
+      <c r="F35" s="59" t="inlineStr"/>
+      <c r="G35" s="59" t="inlineStr"/>
+      <c r="H35" s="59" t="inlineStr"/>
+      <c r="I35" s="59" t="inlineStr"/>
+      <c r="J35" s="60" t="inlineStr"/>
+      <c r="K35" s="59" t="inlineStr"/>
+      <c r="L35" s="59" t="inlineStr"/>
+      <c r="M35" s="59" t="inlineStr"/>
+      <c r="N35" s="59" t="inlineStr"/>
+      <c r="O35" s="59" t="inlineStr"/>
+      <c r="P35" s="59" t="inlineStr"/>
+      <c r="Q35" s="59" t="inlineStr"/>
+      <c r="R35" s="59" t="inlineStr"/>
+      <c r="S35" s="59" t="inlineStr"/>
+      <c r="T35" s="59" t="inlineStr"/>
+      <c r="U35" s="59" t="inlineStr"/>
+      <c r="V35" s="59" t="inlineStr"/>
+      <c r="W35" s="59" t="inlineStr"/>
+      <c r="X35" s="59" t="inlineStr"/>
+      <c r="Y35" s="59" t="inlineStr"/>
+      <c r="Z35" s="59" t="inlineStr"/>
+      <c r="AA35" s="59" t="inlineStr"/>
+      <c r="AB35" s="59" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Internal PROD ECR Implementation</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="57" t="inlineStr"/>
-      <c r="F36" s="58" t="inlineStr"/>
-      <c r="G36" s="57" t="inlineStr"/>
-      <c r="H36" s="14" t="n"/>
-      <c r="I36" s="14" t="n"/>
-      <c r="J36" s="14" t="n"/>
-      <c r="K36" s="14" t="n"/>
-      <c r="L36" s="14" t="n"/>
-      <c r="M36" s="14" t="n"/>
-      <c r="N36" s="14" t="n"/>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="14" t="n"/>
-      <c r="Q36" s="14" t="n"/>
-      <c r="R36" s="14" t="n"/>
-      <c r="S36" s="14" t="n"/>
-      <c r="T36" s="14" t="n"/>
-      <c r="U36" s="14" t="n"/>
-      <c r="V36" s="14" t="n"/>
-      <c r="W36" s="14" t="n"/>
-      <c r="X36" s="14" t="n"/>
-      <c r="Y36" s="14" t="n"/>
-      <c r="Z36" s="14" t="n"/>
-      <c r="AA36" s="14" t="n"/>
-      <c r="AB36" s="14" t="n"/>
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>Bitbucket -&gt; GitLab Migration</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="18" t="n"/>
+      <c r="M36" s="61" t="inlineStr"/>
+      <c r="N36" s="61" t="inlineStr"/>
+      <c r="O36" s="61" t="inlineStr"/>
+      <c r="P36" s="61" t="inlineStr"/>
+      <c r="Q36" s="61" t="inlineStr"/>
+      <c r="R36" s="61" t="inlineStr"/>
+      <c r="S36" s="61" t="inlineStr"/>
+      <c r="T36" s="61" t="inlineStr"/>
+      <c r="U36" s="61" t="inlineStr"/>
+      <c r="V36" s="18" t="n"/>
+      <c r="W36" s="18" t="n"/>
+      <c r="X36" s="18" t="n"/>
+      <c r="Y36" s="18" t="n"/>
+      <c r="Z36" s="18" t="n"/>
+      <c r="AA36" s="18" t="n"/>
+      <c r="AB36" s="18" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n"/>
-      <c r="B37" s="14" t="n"/>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Image Repository</t>
+        </is>
+      </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Internal PROD ECR Migration</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="17" t="n"/>
-      <c r="G37" s="57" t="inlineStr"/>
-      <c r="H37" s="57" t="inlineStr"/>
-      <c r="I37" s="57" t="inlineStr"/>
-      <c r="J37" s="14" t="n"/>
+          <t>Harbor Implementation (CY failover)</t>
+        </is>
+      </c>
+      <c r="D37" s="62" t="inlineStr"/>
+      <c r="E37" s="62" t="inlineStr"/>
+      <c r="F37" s="62" t="inlineStr"/>
+      <c r="G37" s="62" t="inlineStr"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="16" t="n"/>
       <c r="K37" s="14" t="n"/>
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="14" t="n"/>
@@ -2262,62 +2265,54 @@
       <c r="AB37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="n"/>
-      <c r="B38" s="24" t="n"/>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>ECR Baseline</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="25" t="n"/>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="24" t="n"/>
-      <c r="I38" s="59" t="inlineStr"/>
-      <c r="J38" s="60" t="inlineStr"/>
-      <c r="K38" s="60" t="inlineStr"/>
-      <c r="L38" s="60" t="inlineStr"/>
-      <c r="M38" s="60" t="inlineStr"/>
-      <c r="N38" s="60" t="inlineStr"/>
-      <c r="O38" s="60" t="inlineStr"/>
-      <c r="P38" s="60" t="inlineStr"/>
-      <c r="Q38" s="60" t="inlineStr"/>
-      <c r="R38" s="60" t="inlineStr"/>
-      <c r="S38" s="60" t="inlineStr"/>
-      <c r="T38" s="60" t="inlineStr"/>
-      <c r="U38" s="60" t="inlineStr"/>
-      <c r="V38" s="60" t="inlineStr"/>
-      <c r="W38" s="60" t="inlineStr"/>
-      <c r="X38" s="60" t="inlineStr"/>
-      <c r="Y38" s="60" t="inlineStr"/>
-      <c r="Z38" s="60" t="inlineStr"/>
-      <c r="AA38" s="60" t="inlineStr"/>
-      <c r="AB38" s="60" t="inlineStr"/>
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Internal PROD ECR Implementation</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="62" t="inlineStr"/>
+      <c r="F38" s="62" t="inlineStr"/>
+      <c r="G38" s="62" t="inlineStr"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="16" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
+      <c r="O38" s="14" t="n"/>
+      <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14" t="n"/>
+      <c r="R38" s="14" t="n"/>
+      <c r="S38" s="14" t="n"/>
+      <c r="T38" s="14" t="n"/>
+      <c r="U38" s="14" t="n"/>
+      <c r="V38" s="14" t="n"/>
+      <c r="W38" s="14" t="n"/>
+      <c r="X38" s="14" t="n"/>
+      <c r="Y38" s="14" t="n"/>
+      <c r="Z38" s="14" t="n"/>
+      <c r="AA38" s="14" t="n"/>
+      <c r="AB38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Resiliency</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>WEST Standalone Account</t>
-        </is>
-      </c>
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>WEST Asset RMF (0-3)</t>
+          <t>Internal PROD ECR Migration</t>
         </is>
       </c>
       <c r="D39" s="14" t="n"/>
       <c r="E39" s="14" t="n"/>
-      <c r="F39" s="61" t="inlineStr"/>
+      <c r="F39" s="14" t="n"/>
       <c r="G39" s="62" t="inlineStr"/>
       <c r="H39" s="62" t="inlineStr"/>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="14" t="n"/>
+      <c r="I39" s="62" t="inlineStr"/>
+      <c r="J39" s="16" t="n"/>
       <c r="K39" s="14" t="n"/>
       <c r="L39" s="14" t="n"/>
       <c r="M39" s="14" t="n"/>
@@ -2338,96 +2333,100 @@
       <c r="AB39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>WEST Standalone Asset Discovery</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="62" t="inlineStr"/>
-      <c r="I40" s="62" t="inlineStr"/>
-      <c r="J40" s="62" t="inlineStr"/>
-      <c r="K40" s="62" t="inlineStr"/>
-      <c r="L40" s="62" t="inlineStr"/>
-      <c r="M40" s="62" t="inlineStr"/>
-      <c r="N40" s="62" t="inlineStr"/>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="14" t="n"/>
-      <c r="Q40" s="14" t="n"/>
-      <c r="R40" s="14" t="n"/>
-      <c r="S40" s="14" t="n"/>
-      <c r="T40" s="14" t="n"/>
-      <c r="U40" s="14" t="n"/>
-      <c r="V40" s="14" t="n"/>
-      <c r="W40" s="14" t="n"/>
-      <c r="X40" s="14" t="n"/>
-      <c r="Y40" s="14" t="n"/>
-      <c r="Z40" s="14" t="n"/>
-      <c r="AA40" s="14" t="n"/>
-      <c r="AB40" s="14" t="n"/>
+      <c r="A40" s="28" t="n"/>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>ECR Baseline</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="63" t="inlineStr"/>
+      <c r="J40" s="64" t="inlineStr"/>
+      <c r="K40" s="65" t="inlineStr"/>
+      <c r="L40" s="65" t="inlineStr"/>
+      <c r="M40" s="65" t="inlineStr"/>
+      <c r="N40" s="65" t="inlineStr"/>
+      <c r="O40" s="65" t="inlineStr"/>
+      <c r="P40" s="65" t="inlineStr"/>
+      <c r="Q40" s="65" t="inlineStr"/>
+      <c r="R40" s="65" t="inlineStr"/>
+      <c r="S40" s="65" t="inlineStr"/>
+      <c r="T40" s="65" t="inlineStr"/>
+      <c r="U40" s="65" t="inlineStr"/>
+      <c r="V40" s="65" t="inlineStr"/>
+      <c r="W40" s="65" t="inlineStr"/>
+      <c r="X40" s="65" t="inlineStr"/>
+      <c r="Y40" s="65" t="inlineStr"/>
+      <c r="Z40" s="65" t="inlineStr"/>
+      <c r="AA40" s="65" t="inlineStr"/>
+      <c r="AB40" s="65" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n"/>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>WEST Standalone Account Build</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="63" t="inlineStr"/>
-      <c r="K41" s="63" t="inlineStr"/>
-      <c r="L41" s="63" t="inlineStr"/>
-      <c r="M41" s="63" t="inlineStr"/>
-      <c r="N41" s="63" t="inlineStr"/>
-      <c r="O41" s="18" t="n"/>
-      <c r="P41" s="18" t="n"/>
-      <c r="Q41" s="18" t="n"/>
-      <c r="R41" s="18" t="n"/>
-      <c r="S41" s="18" t="n"/>
-      <c r="T41" s="18" t="n"/>
-      <c r="U41" s="18" t="n"/>
-      <c r="V41" s="18" t="n"/>
-      <c r="W41" s="18" t="n"/>
-      <c r="X41" s="18" t="n"/>
-      <c r="Y41" s="18" t="n"/>
-      <c r="Z41" s="18" t="n"/>
-      <c r="AA41" s="18" t="n"/>
-      <c r="AB41" s="18" t="n"/>
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Resiliency</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>WEST Standalone Account</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>WEST Asset RMF (0-3)</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="66" t="inlineStr"/>
+      <c r="G41" s="66" t="inlineStr"/>
+      <c r="H41" s="66" t="inlineStr"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="16" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
+      <c r="N41" s="14" t="n"/>
+      <c r="O41" s="14" t="n"/>
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="14" t="n"/>
+      <c r="R41" s="14" t="n"/>
+      <c r="S41" s="14" t="n"/>
+      <c r="T41" s="14" t="n"/>
+      <c r="U41" s="14" t="n"/>
+      <c r="V41" s="14" t="n"/>
+      <c r="W41" s="14" t="n"/>
+      <c r="X41" s="14" t="n"/>
+      <c r="Y41" s="14" t="n"/>
+      <c r="Z41" s="14" t="n"/>
+      <c r="AA41" s="14" t="n"/>
+      <c r="AB41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n"/>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>EAST -&gt; West Failover</t>
-        </is>
-      </c>
+      <c r="B42" s="14" t="n"/>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>EAST -&gt; WEST Failover Discovery</t>
+          <t>WEST Standalone Asset Discovery</t>
         </is>
       </c>
       <c r="D42" s="14" t="n"/>
       <c r="E42" s="14" t="n"/>
-      <c r="F42" s="17" t="n"/>
+      <c r="F42" s="14" t="n"/>
       <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="64" t="inlineStr"/>
-      <c r="K42" s="64" t="inlineStr"/>
-      <c r="L42" s="64" t="inlineStr"/>
-      <c r="M42" s="14" t="n"/>
-      <c r="N42" s="14" t="n"/>
+      <c r="H42" s="66" t="inlineStr"/>
+      <c r="I42" s="66" t="inlineStr"/>
+      <c r="J42" s="67" t="inlineStr"/>
+      <c r="K42" s="66" t="inlineStr"/>
+      <c r="L42" s="66" t="inlineStr"/>
+      <c r="M42" s="66" t="inlineStr"/>
+      <c r="N42" s="66" t="inlineStr"/>
       <c r="O42" s="14" t="n"/>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
@@ -2444,147 +2443,139 @@
       <c r="AB42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="n"/>
-      <c r="B43" s="14" t="n"/>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>WEST Standalone Account Build</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="68" t="inlineStr"/>
+      <c r="K43" s="69" t="inlineStr"/>
+      <c r="L43" s="69" t="inlineStr"/>
+      <c r="M43" s="69" t="inlineStr"/>
+      <c r="N43" s="69" t="inlineStr"/>
+      <c r="O43" s="18" t="n"/>
+      <c r="P43" s="18" t="n"/>
+      <c r="Q43" s="18" t="n"/>
+      <c r="R43" s="18" t="n"/>
+      <c r="S43" s="18" t="n"/>
+      <c r="T43" s="18" t="n"/>
+      <c r="U43" s="18" t="n"/>
+      <c r="V43" s="18" t="n"/>
+      <c r="W43" s="18" t="n"/>
+      <c r="X43" s="18" t="n"/>
+      <c r="Y43" s="18" t="n"/>
+      <c r="Z43" s="18" t="n"/>
+      <c r="AA43" s="18" t="n"/>
+      <c r="AB43" s="18" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>EAST -&gt; West Failover</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>EAST -&gt; WEST Failover Discovery</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="70" t="inlineStr"/>
+      <c r="K44" s="71" t="inlineStr"/>
+      <c r="L44" s="71" t="inlineStr"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14" t="n"/>
+      <c r="O44" s="14" t="n"/>
+      <c r="P44" s="14" t="n"/>
+      <c r="Q44" s="14" t="n"/>
+      <c r="R44" s="14" t="n"/>
+      <c r="S44" s="14" t="n"/>
+      <c r="T44" s="14" t="n"/>
+      <c r="U44" s="14" t="n"/>
+      <c r="V44" s="14" t="n"/>
+      <c r="W44" s="14" t="n"/>
+      <c r="X44" s="14" t="n"/>
+      <c r="Y44" s="14" t="n"/>
+      <c r="Z44" s="14" t="n"/>
+      <c r="AA44" s="14" t="n"/>
+      <c r="AB44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>EAST -&gt; WEST Failover Implementation</t>
         </is>
       </c>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="14" t="n"/>
-      <c r="I43" s="14" t="n"/>
-      <c r="J43" s="14" t="n"/>
-      <c r="K43" s="14" t="n"/>
-      <c r="L43" s="64" t="inlineStr"/>
-      <c r="M43" s="64" t="inlineStr"/>
-      <c r="N43" s="64" t="inlineStr"/>
-      <c r="O43" s="64" t="inlineStr"/>
-      <c r="P43" s="64" t="inlineStr"/>
-      <c r="Q43" s="64" t="inlineStr"/>
-      <c r="R43" s="64" t="inlineStr"/>
-      <c r="S43" s="64" t="inlineStr"/>
-      <c r="T43" s="64" t="inlineStr"/>
-      <c r="U43" s="14" t="n"/>
-      <c r="V43" s="14" t="n"/>
-      <c r="W43" s="14" t="n"/>
-      <c r="X43" s="14" t="n"/>
-      <c r="Y43" s="14" t="n"/>
-      <c r="Z43" s="14" t="n"/>
-      <c r="AA43" s="14" t="n"/>
-      <c r="AB43" s="14" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="n"/>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="16" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="71" t="inlineStr"/>
+      <c r="M45" s="71" t="inlineStr"/>
+      <c r="N45" s="71" t="inlineStr"/>
+      <c r="O45" s="71" t="inlineStr"/>
+      <c r="P45" s="71" t="inlineStr"/>
+      <c r="Q45" s="71" t="inlineStr"/>
+      <c r="R45" s="71" t="inlineStr"/>
+      <c r="S45" s="71" t="inlineStr"/>
+      <c r="T45" s="71" t="inlineStr"/>
+      <c r="U45" s="14" t="n"/>
+      <c r="V45" s="14" t="n"/>
+      <c r="W45" s="14" t="n"/>
+      <c r="X45" s="14" t="n"/>
+      <c r="Y45" s="14" t="n"/>
+      <c r="Z45" s="14" t="n"/>
+      <c r="AA45" s="14" t="n"/>
+      <c r="AB45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="n"/>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>EAST -&gt; WEST Failover Testing</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="20" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="18" t="n"/>
-      <c r="I44" s="18" t="n"/>
-      <c r="J44" s="18" t="n"/>
-      <c r="K44" s="18" t="n"/>
-      <c r="L44" s="18" t="n"/>
-      <c r="M44" s="18" t="n"/>
-      <c r="N44" s="18" t="n"/>
-      <c r="O44" s="18" t="n"/>
-      <c r="P44" s="18" t="n"/>
-      <c r="Q44" s="18" t="n"/>
-      <c r="R44" s="18" t="n"/>
-      <c r="S44" s="65" t="inlineStr"/>
-      <c r="T44" s="65" t="inlineStr"/>
-      <c r="U44" s="65" t="inlineStr"/>
-      <c r="V44" s="65" t="inlineStr"/>
-      <c r="W44" s="65" t="inlineStr"/>
-      <c r="X44" s="18" t="n"/>
-      <c r="Y44" s="18" t="n"/>
-      <c r="Z44" s="18" t="n"/>
-      <c r="AA44" s="18" t="n"/>
-      <c r="AB44" s="18" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="n"/>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>FIS Implementation</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>FIS Support</t>
-        </is>
-      </c>
-      <c r="D45" s="66" t="inlineStr"/>
-      <c r="E45" s="66" t="inlineStr"/>
-      <c r="F45" s="67" t="inlineStr"/>
-      <c r="G45" s="66" t="inlineStr"/>
-      <c r="H45" s="66" t="inlineStr"/>
-      <c r="I45" s="66" t="inlineStr"/>
-      <c r="J45" s="66" t="inlineStr"/>
-      <c r="K45" s="66" t="inlineStr"/>
-      <c r="L45" s="66" t="inlineStr"/>
-      <c r="M45" s="66" t="inlineStr"/>
-      <c r="N45" s="66" t="inlineStr"/>
-      <c r="O45" s="66" t="inlineStr"/>
-      <c r="P45" s="66" t="inlineStr"/>
-      <c r="Q45" s="66" t="inlineStr"/>
-      <c r="R45" s="66" t="inlineStr"/>
-      <c r="S45" s="66" t="inlineStr"/>
-      <c r="T45" s="66" t="inlineStr"/>
-      <c r="U45" s="66" t="inlineStr"/>
-      <c r="V45" s="66" t="inlineStr"/>
-      <c r="W45" s="66" t="inlineStr"/>
-      <c r="X45" s="66" t="inlineStr"/>
-      <c r="Y45" s="66" t="inlineStr"/>
-      <c r="Z45" s="66" t="inlineStr"/>
-      <c r="AA45" s="66" t="inlineStr"/>
-      <c r="AB45" s="66" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="68" t="inlineStr">
-        <is>
-          <t>Core Support Services</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>AI Enablements</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>Platform AI assistant beta</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
       <c r="E46" s="18" t="n"/>
-      <c r="F46" s="20" t="n"/>
+      <c r="F46" s="18" t="n"/>
       <c r="G46" s="18" t="n"/>
       <c r="H46" s="18" t="n"/>
       <c r="I46" s="18" t="n"/>
-      <c r="J46" s="18" t="n"/>
-      <c r="K46" s="69" t="inlineStr"/>
-      <c r="L46" s="69" t="inlineStr"/>
-      <c r="M46" s="69" t="inlineStr"/>
-      <c r="N46" s="69" t="inlineStr"/>
-      <c r="O46" s="69" t="inlineStr"/>
-      <c r="P46" s="69" t="inlineStr"/>
-      <c r="Q46" s="69" t="inlineStr"/>
-      <c r="R46" s="69" t="inlineStr"/>
-      <c r="S46" s="69" t="inlineStr"/>
-      <c r="T46" s="18" t="n"/>
-      <c r="U46" s="18" t="n"/>
-      <c r="V46" s="18" t="n"/>
-      <c r="W46" s="18" t="n"/>
+      <c r="J46" s="20" t="n"/>
+      <c r="K46" s="18" t="n"/>
+      <c r="L46" s="18" t="n"/>
+      <c r="M46" s="18" t="n"/>
+      <c r="N46" s="18" t="n"/>
+      <c r="O46" s="18" t="n"/>
+      <c r="P46" s="18" t="n"/>
+      <c r="Q46" s="18" t="n"/>
+      <c r="R46" s="18" t="n"/>
+      <c r="S46" s="72" t="inlineStr"/>
+      <c r="T46" s="72" t="inlineStr"/>
+      <c r="U46" s="72" t="inlineStr"/>
+      <c r="V46" s="72" t="inlineStr"/>
+      <c r="W46" s="72" t="inlineStr"/>
       <c r="X46" s="18" t="n"/>
       <c r="Y46" s="18" t="n"/>
       <c r="Z46" s="18" t="n"/>
@@ -2592,260 +2583,341 @@
       <c r="AB46" s="18" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="n"/>
+      <c r="A47" s="28" t="n"/>
       <c r="B47" s="8" t="inlineStr">
         <is>
+          <t>FIS Implementation</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>FIS Support</t>
+        </is>
+      </c>
+      <c r="D47" s="73" t="inlineStr"/>
+      <c r="E47" s="73" t="inlineStr"/>
+      <c r="F47" s="73" t="inlineStr"/>
+      <c r="G47" s="73" t="inlineStr"/>
+      <c r="H47" s="73" t="inlineStr"/>
+      <c r="I47" s="73" t="inlineStr"/>
+      <c r="J47" s="74" t="inlineStr"/>
+      <c r="K47" s="73" t="inlineStr"/>
+      <c r="L47" s="73" t="inlineStr"/>
+      <c r="M47" s="73" t="inlineStr"/>
+      <c r="N47" s="73" t="inlineStr"/>
+      <c r="O47" s="73" t="inlineStr"/>
+      <c r="P47" s="73" t="inlineStr"/>
+      <c r="Q47" s="73" t="inlineStr"/>
+      <c r="R47" s="73" t="inlineStr"/>
+      <c r="S47" s="73" t="inlineStr"/>
+      <c r="T47" s="73" t="inlineStr"/>
+      <c r="U47" s="73" t="inlineStr"/>
+      <c r="V47" s="73" t="inlineStr"/>
+      <c r="W47" s="73" t="inlineStr"/>
+      <c r="X47" s="73" t="inlineStr"/>
+      <c r="Y47" s="73" t="inlineStr"/>
+      <c r="Z47" s="73" t="inlineStr"/>
+      <c r="AA47" s="73" t="inlineStr"/>
+      <c r="AB47" s="73" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="75" t="inlineStr">
+        <is>
+          <t>Core Support Services</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>AI Enablements</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Platform AI assistant beta</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="18" t="n"/>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="20" t="n"/>
+      <c r="K48" s="76" t="inlineStr"/>
+      <c r="L48" s="76" t="inlineStr"/>
+      <c r="M48" s="76" t="inlineStr"/>
+      <c r="N48" s="76" t="inlineStr"/>
+      <c r="O48" s="76" t="inlineStr"/>
+      <c r="P48" s="76" t="inlineStr"/>
+      <c r="Q48" s="76" t="inlineStr"/>
+      <c r="R48" s="76" t="inlineStr"/>
+      <c r="S48" s="76" t="inlineStr"/>
+      <c r="T48" s="18" t="n"/>
+      <c r="U48" s="18" t="n"/>
+      <c r="V48" s="18" t="n"/>
+      <c r="W48" s="18" t="n"/>
+      <c r="X48" s="18" t="n"/>
+      <c r="Y48" s="18" t="n"/>
+      <c r="Z48" s="18" t="n"/>
+      <c r="AA48" s="18" t="n"/>
+      <c r="AB48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Unified platform portal</t>
         </is>
       </c>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="70" t="inlineStr"/>
-      <c r="G47" s="71" t="inlineStr"/>
-      <c r="H47" s="71" t="inlineStr"/>
-      <c r="I47" s="71" t="inlineStr"/>
-      <c r="J47" s="71" t="inlineStr"/>
-      <c r="K47" s="24" t="n"/>
-      <c r="L47" s="24" t="n"/>
-      <c r="M47" s="24" t="n"/>
-      <c r="N47" s="24" t="n"/>
-      <c r="O47" s="24" t="n"/>
-      <c r="P47" s="24" t="n"/>
-      <c r="Q47" s="24" t="n"/>
-      <c r="R47" s="24" t="n"/>
-      <c r="S47" s="24" t="n"/>
-      <c r="T47" s="24" t="n"/>
-      <c r="U47" s="24" t="n"/>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="24" t="n"/>
-      <c r="X47" s="24" t="n"/>
-      <c r="Y47" s="24" t="n"/>
-      <c r="Z47" s="24" t="n"/>
-      <c r="AA47" s="24" t="n"/>
-      <c r="AB47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>FVEY C2S Core</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>FVEY C2S Core</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>Cross-domain service mesh</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="n"/>
-      <c r="E48" s="24" t="n"/>
-      <c r="F48" s="25" t="n"/>
-      <c r="G48" s="24" t="n"/>
-      <c r="H48" s="72" t="inlineStr"/>
-      <c r="I48" s="72" t="inlineStr"/>
-      <c r="J48" s="72" t="inlineStr"/>
-      <c r="K48" s="72" t="inlineStr"/>
-      <c r="L48" s="72" t="inlineStr"/>
-      <c r="M48" s="72" t="inlineStr"/>
-      <c r="N48" s="72" t="inlineStr"/>
-      <c r="O48" s="24" t="n"/>
-      <c r="P48" s="24" t="n"/>
-      <c r="Q48" s="24" t="n"/>
-      <c r="R48" s="24" t="n"/>
-      <c r="S48" s="24" t="n"/>
-      <c r="T48" s="24" t="n"/>
-      <c r="U48" s="24" t="n"/>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="24" t="n"/>
-      <c r="X48" s="24" t="n"/>
-      <c r="Y48" s="24" t="n"/>
-      <c r="Z48" s="24" t="n"/>
-      <c r="AA48" s="24" t="n"/>
-      <c r="AB48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>FVEY C2S Support</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>FVEY C2S Support</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>FVEY compliance automation</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="24" t="n"/>
-      <c r="F49" s="25" t="n"/>
-      <c r="G49" s="24" t="n"/>
-      <c r="H49" s="24" t="n"/>
-      <c r="I49" s="73" t="inlineStr"/>
-      <c r="J49" s="73" t="inlineStr"/>
-      <c r="K49" s="73" t="inlineStr"/>
-      <c r="L49" s="73" t="inlineStr"/>
-      <c r="M49" s="73" t="inlineStr"/>
-      <c r="N49" s="73" t="inlineStr"/>
-      <c r="O49" s="73" t="inlineStr"/>
-      <c r="P49" s="73" t="inlineStr"/>
-      <c r="Q49" s="24" t="n"/>
-      <c r="R49" s="24" t="n"/>
-      <c r="S49" s="24" t="n"/>
-      <c r="T49" s="24" t="n"/>
-      <c r="U49" s="24" t="n"/>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="24" t="n"/>
-      <c r="X49" s="24" t="n"/>
-      <c r="Y49" s="24" t="n"/>
-      <c r="Z49" s="24" t="n"/>
-      <c r="AA49" s="24" t="n"/>
-      <c r="AB49" s="24" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="77" t="inlineStr"/>
+      <c r="G49" s="77" t="inlineStr"/>
+      <c r="H49" s="77" t="inlineStr"/>
+      <c r="I49" s="77" t="inlineStr"/>
+      <c r="J49" s="78" t="inlineStr"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="28" t="n"/>
+      <c r="M49" s="28" t="n"/>
+      <c r="N49" s="28" t="n"/>
+      <c r="O49" s="28" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n"/>
+      <c r="R49" s="28" t="n"/>
+      <c r="S49" s="28" t="n"/>
+      <c r="T49" s="28" t="n"/>
+      <c r="U49" s="28" t="n"/>
+      <c r="V49" s="28" t="n"/>
+      <c r="W49" s="28" t="n"/>
+      <c r="X49" s="28" t="n"/>
+      <c r="Y49" s="28" t="n"/>
+      <c r="Z49" s="28" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>DEV C2S Core</t>
+          <t>FVEY C2S Core</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>DEV C2S Core</t>
+          <t>FVEY C2S Core</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>DEV enclave platform baseline</t>
-        </is>
-      </c>
-      <c r="D50" s="74" t="inlineStr"/>
-      <c r="E50" s="74" t="inlineStr"/>
-      <c r="F50" s="75" t="inlineStr"/>
-      <c r="G50" s="74" t="inlineStr"/>
-      <c r="H50" s="74" t="inlineStr"/>
-      <c r="I50" s="74" t="inlineStr"/>
-      <c r="J50" s="74" t="inlineStr"/>
-      <c r="K50" s="24" t="n"/>
-      <c r="L50" s="24" t="n"/>
-      <c r="M50" s="24" t="n"/>
-      <c r="N50" s="24" t="n"/>
-      <c r="O50" s="24" t="n"/>
-      <c r="P50" s="24" t="n"/>
-      <c r="Q50" s="24" t="n"/>
-      <c r="R50" s="24" t="n"/>
-      <c r="S50" s="24" t="n"/>
-      <c r="T50" s="24" t="n"/>
-      <c r="U50" s="24" t="n"/>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="24" t="n"/>
-      <c r="X50" s="24" t="n"/>
-      <c r="Y50" s="24" t="n"/>
-      <c r="Z50" s="24" t="n"/>
-      <c r="AA50" s="24" t="n"/>
-      <c r="AB50" s="24" t="n"/>
+          <t>Cross-domain service mesh</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="79" t="inlineStr"/>
+      <c r="I50" s="79" t="inlineStr"/>
+      <c r="J50" s="80" t="inlineStr"/>
+      <c r="K50" s="79" t="inlineStr"/>
+      <c r="L50" s="79" t="inlineStr"/>
+      <c r="M50" s="79" t="inlineStr"/>
+      <c r="N50" s="79" t="inlineStr"/>
+      <c r="O50" s="28" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n"/>
+      <c r="R50" s="28" t="n"/>
+      <c r="S50" s="28" t="n"/>
+      <c r="T50" s="28" t="n"/>
+      <c r="U50" s="28" t="n"/>
+      <c r="V50" s="28" t="n"/>
+      <c r="W50" s="28" t="n"/>
+      <c r="X50" s="28" t="n"/>
+      <c r="Y50" s="28" t="n"/>
+      <c r="Z50" s="28" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
+          <t>FVEY C2S Support</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>FVEY C2S Support</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>FVEY compliance automation</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="81" t="inlineStr"/>
+      <c r="J51" s="82" t="inlineStr"/>
+      <c r="K51" s="81" t="inlineStr"/>
+      <c r="L51" s="81" t="inlineStr"/>
+      <c r="M51" s="81" t="inlineStr"/>
+      <c r="N51" s="81" t="inlineStr"/>
+      <c r="O51" s="81" t="inlineStr"/>
+      <c r="P51" s="81" t="inlineStr"/>
+      <c r="Q51" s="28" t="n"/>
+      <c r="R51" s="28" t="n"/>
+      <c r="S51" s="28" t="n"/>
+      <c r="T51" s="28" t="n"/>
+      <c r="U51" s="28" t="n"/>
+      <c r="V51" s="28" t="n"/>
+      <c r="W51" s="28" t="n"/>
+      <c r="X51" s="28" t="n"/>
+      <c r="Y51" s="28" t="n"/>
+      <c r="Z51" s="28" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>DEV C2S Core</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>DEV C2S Core</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>DEV enclave platform baseline</t>
+        </is>
+      </c>
+      <c r="D52" s="83" t="inlineStr"/>
+      <c r="E52" s="83" t="inlineStr"/>
+      <c r="F52" s="83" t="inlineStr"/>
+      <c r="G52" s="83" t="inlineStr"/>
+      <c r="H52" s="83" t="inlineStr"/>
+      <c r="I52" s="83" t="inlineStr"/>
+      <c r="J52" s="84" t="inlineStr"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="28" t="n"/>
+      <c r="M52" s="28" t="n"/>
+      <c r="N52" s="28" t="n"/>
+      <c r="O52" s="28" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n"/>
+      <c r="R52" s="28" t="n"/>
+      <c r="S52" s="28" t="n"/>
+      <c r="T52" s="28" t="n"/>
+      <c r="U52" s="28" t="n"/>
+      <c r="V52" s="28" t="n"/>
+      <c r="W52" s="28" t="n"/>
+      <c r="X52" s="28" t="n"/>
+      <c r="Y52" s="28" t="n"/>
+      <c r="Z52" s="28" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
           <t>DEV C2S Support</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>DEV C2S Support</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>DEV enclave operational tooling</t>
         </is>
       </c>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="24" t="n"/>
-      <c r="F51" s="25" t="n"/>
-      <c r="G51" s="76" t="inlineStr"/>
-      <c r="H51" s="76" t="inlineStr"/>
-      <c r="I51" s="76" t="inlineStr"/>
-      <c r="J51" s="76" t="inlineStr"/>
-      <c r="K51" s="76" t="inlineStr"/>
-      <c r="L51" s="76" t="inlineStr"/>
-      <c r="M51" s="76" t="inlineStr"/>
-      <c r="N51" s="24" t="n"/>
-      <c r="O51" s="24" t="n"/>
-      <c r="P51" s="24" t="n"/>
-      <c r="Q51" s="24" t="n"/>
-      <c r="R51" s="24" t="n"/>
-      <c r="S51" s="24" t="n"/>
-      <c r="T51" s="24" t="n"/>
-      <c r="U51" s="24" t="n"/>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="24" t="n"/>
-      <c r="X51" s="24" t="n"/>
-      <c r="Y51" s="24" t="n"/>
-      <c r="Z51" s="24" t="n"/>
-      <c r="AA51" s="24" t="n"/>
-      <c r="AB51" s="24" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D53" s="28" t="n"/>
+      <c r="E53" s="28" t="n"/>
+      <c r="F53" s="28" t="n"/>
+      <c r="G53" s="85" t="inlineStr"/>
+      <c r="H53" s="85" t="inlineStr"/>
+      <c r="I53" s="85" t="inlineStr"/>
+      <c r="J53" s="86" t="inlineStr"/>
+      <c r="K53" s="85" t="inlineStr"/>
+      <c r="L53" s="85" t="inlineStr"/>
+      <c r="M53" s="85" t="inlineStr"/>
+      <c r="N53" s="28" t="n"/>
+      <c r="O53" s="28" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n"/>
+      <c r="R53" s="28" t="n"/>
+      <c r="S53" s="28" t="n"/>
+      <c r="T53" s="28" t="n"/>
+      <c r="U53" s="28" t="n"/>
+      <c r="V53" s="28" t="n"/>
+      <c r="W53" s="28" t="n"/>
+      <c r="X53" s="28" t="n"/>
+      <c r="Y53" s="28" t="n"/>
+      <c r="Z53" s="28" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="77" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="87" t="inlineStr">
         <is>
           <t>Baseline (primary offering)</t>
         </is>
       </c>
-      <c r="B55" s="78" t="inlineStr">
+      <c r="B57" s="88" t="inlineStr">
         <is>
           <t>Green left accent</t>
         </is>
       </c>
-      <c r="C55" s="79" t="inlineStr">
+      <c r="C57" s="89" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D55" s="78" t="inlineStr">
+      <c r="D57" s="88" t="inlineStr">
         <is>
           <t>Orange dashed left accent</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B15:B18"/>
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A13:A38"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B9:B12"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B28:B32"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A15:A40"/>
+    <mergeCell ref="A5:A14"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B35:B36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2857,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2870,37 +2942,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="90" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B1" s="80" t="inlineStr">
+      <c r="B1" s="90" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="C1" s="80" t="inlineStr">
+      <c r="C1" s="90" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="D1" s="80" t="inlineStr">
+      <c r="D1" s="90" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="E1" s="80" t="inlineStr">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="F1" s="80" t="inlineStr">
+      <c r="F1" s="90" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="G1" s="80" t="inlineStr">
+      <c r="G1" s="90" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -3208,75 +3280,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Core Services</t>
+          <t>Onboarding Tenant Apps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kubernetes (Rancher)</t>
+          <t>Onboarding Tenant Apps</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rancher RKE1 support</t>
+          <t>NEW 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Initial EKS support through R2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Core Services</t>
+          <t>Onboarding Tenant Apps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kubernetes (Rancher)</t>
+          <t>Onboarding Tenant Apps</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rancher RKE2 development</t>
+          <t>NEW 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Initial EKS support through R2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3292,12 +3356,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rancher RKE2 Tenant Migration</t>
+          <t>Rancher RKE1 support</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3329,17 +3393,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rancher RKE2 Tenant Support</t>
+          <t>Rancher RKE2 development</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3361,17 +3425,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kubernetes (EKS)</t>
+          <t>Kubernetes (Rancher)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EKS v1 support</t>
+          <t>Rancher RKE2 Tenant Migration</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3386,7 +3450,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optional</t>
         </is>
       </c>
     </row>
@@ -3398,32 +3462,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kubernetes (EKS)</t>
+          <t>Kubernetes (Rancher)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AL2023 AMI hardening and STIG</t>
+          <t>Rancher RKE2 Tenant Support</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AMI hardening and STIG compliance</t>
+          <t>Initial EKS support through R2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optional</t>
         </is>
       </c>
     </row>
@@ -3440,22 +3504,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EKS v2 config</t>
+          <t>EKS v1 support</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EKS v2 configuration and rollout</t>
+          <t>Initial EKS support through R2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3477,22 +3541,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi-cluster federation</t>
+          <t>AL2023 AMI hardening and STIG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enables regional failover</t>
+          <t>AMI hardening and STIG compliance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3509,12 +3573,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kubernetes (EKS Auto)</t>
+          <t>Kubernetes (EKS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EKS Auto Discovery</t>
+          <t>EKS v2 config</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3529,11 +3593,13 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Read up on EKS auto, meet w AWS for questions, deliver findings to client</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v/>
+          <t>EKS v2 configuration and rollout</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -3544,31 +3610,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kubernetes (EKS Auto)</t>
+          <t>Kubernetes (EKS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EKS Auto Platform Implementation</t>
+          <t>Multi-cluster federation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Test EKS Auto, will have to have complete for Tenant X by 07-01</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v/>
+          <t>Enables regional failover</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3579,33 +3647,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Observability</t>
+          <t>Kubernetes (EKS Auto)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elastic Support</t>
+          <t>EKS Auto Discovery</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard observability stack</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>baseline</t>
-        </is>
+          <t>Read up on EKS auto, meet w AWS for questions, deliver findings to client</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -3616,33 +3682,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Observability</t>
+          <t>Kubernetes (EKS Auto)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prometheus/Grafana Support</t>
+          <t>EKS Auto Platform Implementation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard observability stack</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
+          <t>Test EKS Auto, will have to have complete for Tenant X by 07-01</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -3658,7 +3722,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prometheus/Grafana Add-ons</t>
+          <t>Elastic Support</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3678,7 +3742,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3759,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elastic Support</t>
+          <t>Prometheus/Grafana Support</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>May 2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3732,19 +3796,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prometheus/Grafana Support</t>
+          <t>Prometheus/Grafana Add-ons</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Standard observability stack</t>
@@ -3752,7 +3816,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optional</t>
         </is>
       </c>
     </row>
@@ -3764,32 +3828,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OAuth</t>
+          <t>Observability</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Keycloak OAUTH2 Support</t>
+          <t>Elastic Support</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>External IdP federation</t>
+          <t>Standard observability stack</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optional</t>
         </is>
       </c>
     </row>
@@ -3801,32 +3865,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OAuth</t>
+          <t>Observability</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>F5 Support</t>
+          <t>Prometheus/Grafana Support</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Removes dependency of IDAMS LDAP Password and resource configuration and O&amp;M</t>
+          <t>Standard observability stack</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
@@ -3843,12 +3907,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>F5/DEX/OAUTH2 Developmment</t>
+          <t>Keycloak OAUTH2 Support</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3858,7 +3922,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Effectively replaces Keycloak so that we can move forward with less external dependencies and a lighter weight baseline to reduce O&amp;M</t>
+          <t>External IdP federation</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3880,27 +3944,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>F5/DEX/OAUTH2 Support</t>
+          <t>F5 Support</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Effectively replaces Keycloak so that we can move forward with less external dependencies and a lighter weight baseline to reduce O&amp;M</t>
+          <t>Removes dependency of IDAMS LDAP Password and resource configuration and O&amp;M</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optional</t>
         </is>
       </c>
     </row>
@@ -3917,17 +3981,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>F5/DEX/OAUTH2 Support</t>
+          <t>F5/DEX/OAUTH2 Developmment</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>May 2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3949,17 +4013,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CICD</t>
+          <t>OAuth</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GitLab Support</t>
+          <t>F5/DEX/OAUTH2 Support</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3969,7 +4033,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Standardized pipelines across tenants, hardenening scripts, devops tools like certbot</t>
+          <t>Effectively replaces Keycloak so that we can move forward with less external dependencies and a lighter weight baseline to reduce O&amp;M</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3986,31 +4050,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CICD</t>
+          <t>OAuth</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bitbucket -&gt; GitLab Migration</t>
+          <t>F5/DEX/OAUTH2 Support</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>There might not be much of a reason to migrate from bitbucket other than consistency but it needs to be understood how we can keep the tf state the same if we execute migration</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v/>
+          <t>Effectively replaces Keycloak so that we can move forward with less external dependencies and a lighter weight baseline to reduce O&amp;M</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -4021,12 +4087,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Image Repository</t>
+          <t>CICD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Harbor Implementation (CY failover)</t>
+          <t>GitLab Support</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4036,16 +4102,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CY failover solution to maintain platform conainer images</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v/>
+          <t>Standardized pipelines across tenants, hardenening scripts, devops tools like certbot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -4056,27 +4124,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Image Repository</t>
+          <t>CICD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Internal PROD ECR Implementation</t>
+          <t>Bitbucket -&gt; GitLab Migration</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>May 2027</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Test AMI pipeline images to ECR</t>
+          <t>There might not be much of a reason to migrate from bitbucket other than consistency but it needs to be understood how we can keep the tf state the same if we execute migration</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4096,22 +4164,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Internal PROD ECR Migration</t>
+          <t>Harbor Implementation (CY failover)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Migrate all platform images to ECR</t>
+          <t>CY failover solution to maintain platform conainer images</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4131,59 +4199,57 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ECR Baseline</t>
+          <t>Internal PROD ECR Implementation</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>This eliminates the dependency of CY and will deprecate the need of Harbor such to improve platform efficiencies by utilizing cloud native solutions and reduce resources</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>baseline</t>
-        </is>
+          <t>Test AMI pipeline images to ECR</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Resiliency</t>
+          <t>Core Services</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WEST Standalone Account</t>
+          <t>Image Repository</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WEST Asset RMF (0-3)</t>
+          <t>Internal PROD ECR Migration</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Create WEST asset and get account IATT</t>
+          <t>Migrate all platform images to ECR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4193,36 +4259,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Resiliency</t>
+          <t>Core Services</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WEST Standalone Account</t>
+          <t>Image Repository</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WEST Standalone Asset Discovery</t>
+          <t>ECR Baseline</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Dec 2027</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Discover phase of west standalone</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v/>
+          <t>This eliminates the dependency of CY and will deprecate the need of Harbor such to improve platform efficiencies by utilizing cloud native solutions and reduce resources</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -4238,22 +4306,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WEST Standalone Account Build</t>
+          <t>WEST Asset RMF (0-3)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wrap up standalone west potential</t>
+          <t>Create WEST asset and get account IATT</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4268,26 +4336,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EAST -&gt; West Failover</t>
+          <t>WEST Standalone Account</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EAST -&gt; WEST Failover Discovery</t>
+          <t>WEST Standalone Asset Discovery</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v/>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Discover phase of west standalone</t>
+        </is>
       </c>
       <c r="G40" t="n">
         <v/>
@@ -4301,26 +4371,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EAST -&gt; West Failover</t>
+          <t>WEST Standalone Account</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EAST -&gt; WEST Failover Implementation</t>
+          <t>WEST Standalone Account Build</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v/>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Wrap up standalone west potential</t>
+        </is>
       </c>
       <c r="G41" t="n">
         <v/>
@@ -4339,17 +4411,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EAST -&gt; WEST Failover Testing</t>
+          <t>EAST -&gt; WEST Failover Discovery</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4367,22 +4439,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FIS Implementation</t>
+          <t>EAST -&gt; West Failover</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FIS Support</t>
+          <t>EAST -&gt; WEST Failover Implementation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>Apr 2027</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4395,33 +4467,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Core Support Services</t>
+          <t>Resiliency</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AI Enablements</t>
+          <t>EAST -&gt; West Failover</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Platform AI assistant beta</t>
+          <t>EAST -&gt; WEST Failover Testing</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Mar 2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Operator productivity tooling</t>
-        </is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
       <c r="G44" t="n">
         <v/>
@@ -4430,33 +4500,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Core Support Services</t>
+          <t>Resiliency</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Landing Page</t>
+          <t>FIS Implementation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unified platform portal</t>
+          <t>FIS Support</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Single entry point for tenants</t>
-        </is>
+          <t>Dec 2027</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
       <c r="G45" t="n">
         <v/>
@@ -4465,32 +4533,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FVEY C2S Core</t>
+          <t>Core Support Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FVEY C2S Core</t>
+          <t>AI Enablements</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cross-domain service mesh</t>
+          <t>Platform AI assistant beta</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Mar 2027</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Secure multi-domain networking</t>
+          <t>Operator productivity tooling</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -4500,32 +4568,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FVEY C2S Support</t>
+          <t>Core Support Services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FVEY C2S Support</t>
+          <t>Landing Page</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FVEY compliance automation</t>
+          <t>Unified platform portal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Continuous compliance enforcement</t>
+          <t>Single entry point for tenants</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -4535,32 +4603,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DEV C2S Core</t>
+          <t>FVEY C2S Core</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DEV C2S Core</t>
+          <t>FVEY C2S Core</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DEV enclave platform baseline</t>
+          <t>Cross-domain service mesh</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Oct 2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Initial DEV enclave rollout</t>
+          <t>Secure multi-domain networking</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -4570,35 +4638,105 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>FVEY C2S Support</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FVEY C2S Support</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FVEY compliance automation</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Continuous compliance enforcement</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DEV C2S Core</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DEV C2S Core</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEV enclave platform baseline</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Initial DEV enclave rollout</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>DEV C2S Support</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>DEV C2S Support</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>DEV enclave operational tooling</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Logging monitoring and support tooling</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="G51" t="n">
         <v/>
       </c>
     </row>
@@ -4622,17 +4760,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="90" t="inlineStr">
         <is>
           <t>release</t>
         </is>
       </c>
-      <c r="B1" s="80" t="inlineStr">
+      <c r="B1" s="90" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="C1" s="80" t="inlineStr">
+      <c r="C1" s="90" t="inlineStr">
         <is>
           <t>end</t>
         </is>
@@ -4658,7 +4796,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4675,7 +4813,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4692,7 +4830,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4709,7 +4847,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4726,7 +4864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4743,7 +4881,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4760,7 +4898,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
